--- a/public/modelo-importacao-clientes.xlsx
+++ b/public/modelo-importacao-clientes.xlsx
@@ -1,59 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Instruções" sheetId="1" r:id="rId1"/>
-    <sheet name="Clientes" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Instruções" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Clientes" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clientes'!$A$1:$O$1</definedName>
-  </definedNames>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>Layout de Importação de Clientes — Contabilidade by Attentive</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Preencha uma linha por empresa na aba “Clientes”. Não apague o cabeçalho.</t>
+  </si>
+  <si>
+    <t>Matriz e filiais ficam na mesma aba: a coluna “Tipo” diz se é Matriz ou Filial, e “Código da Matriz” liga a filial à matriz (deixe em branco na linha da matriz).</t>
+  </si>
+  <si>
+    <t>CNPJ é a chave do cadastro — não é possível cadastrar dois clientes com o mesmo CNPJ.</t>
+  </si>
+  <si>
+    <t>Prazo de entrega do balancete: dia do mês (5, 10, 15, 20, 25 ou 30). É esse prazo que alimenta o painel de prazos do dashboard.</t>
+  </si>
+  <si>
+    <t>Sistema financeiro (coluna M): qual sistema o cliente usa — ex.: Conta Azul.</t>
+  </si>
+  <si>
+    <t>Integração financeira (coluna N): “Excel” habilita a importação por Excel na plataforma; “Sistema” indica que o financeiro vem do próprio sistema (coluna M); “Não usa” quando não há integração.</t>
+  </si>
+  <si>
+    <t>Cadastro de Clientes — uma linha por empresa (matriz e filiais)</t>
+  </si>
+  <si>
+    <t>Código no Domínio</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Código da Matriz</t>
+  </si>
+  <si>
+    <t>Razão Social</t>
+  </si>
+  <si>
+    <t>Nome Fantasia</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
+  </si>
+  <si>
+    <t>Regime Tributário</t>
+  </si>
+  <si>
+    <t>Tipo de Fechamento</t>
+  </si>
+  <si>
+    <t>Prazo de entrega do balancete</t>
+  </si>
+  <si>
+    <t>Competência de início (mm/aaaa)</t>
+  </si>
+  <si>
+    <t>Fazer carga inicial de saldos</t>
+  </si>
+  <si>
+    <t>Coleta automática do razão</t>
+  </si>
+  <si>
+    <t>Sistema financeiro</t>
+  </si>
+  <si>
+    <t>Integração financeira</t>
+  </si>
+  <si>
+    <t>Analista responsável</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1B2A4A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="FF333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B2A4A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,15 +146,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2857500" cy="466725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -400,302 +540,389 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="118" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="str">
-        <v>Layout de Importação de Clientes — Plataforma Contábil</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" t="str">
-        <v/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" t="str">
-        <v>O que esta planilha importa</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="str">
-        <v>Apenas o cadastro do cliente: matriz e filiais. A chave é o CÓDIGO NO DOMÍNIO — não criamos código novo.</v>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="str">
-        <v>Matriz e filiais ficam na mesma aba "Clientes", uma por linha. A coluna "Tipo" diz se é Matriz ou Filial, e "Código da Matriz" liga a filial à matriz (em branco na linha da matriz).</v>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="str">
-        <v>Sistema financeiro = qual sistema o cliente usa (ou "Não usa"). Integração financeira = "Sistema" ou "Excel". O que for EXCEL habilita a Integração Financeira da plataforma (joga o arquivo &gt; contabiliza &gt; gera o arquivo do Domínio).</v>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="str">
-        <v/>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="str">
-        <v>O resto é importado dentro da plataforma</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="str">
-        <v>Contatos, Plano de Contas, De/Para, Apelidos e Particularidades NÃO vão nesta planilha. Eles são importados direto na Base de Informações do cliente, cada um com a sua VIGÊNCIA — e a plataforma registra quem importou e quando.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="str">
-        <v>Cada nova importação cria uma nova vigência; as anteriores ficam no histórico, nada é sobrescrito.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="str">
-        <v>As linhas em cinza/itálico são EXEMPLO (Euro Brake). Apague e ponha os seus dados. Pode acrescentar colunas à vontade.</v>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="B1:B12"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P203"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="21.83203125" customWidth="1"/>
-    <col min="9" max="9" width="32.83203125" customWidth="1"/>
-    <col min="10" max="10" width="34.83203125" customWidth="1"/>
-    <col min="11" max="11" width="32.83203125" customWidth="1"/>
-    <col min="12" max="12" width="29.83203125" customWidth="1"/>
-    <col min="13" max="13" width="21.83203125" customWidth="1"/>
-    <col min="14" max="14" width="24.83203125" customWidth="1"/>
-    <col min="15" max="15" width="23.83203125" customWidth="1"/>
-    <col min="16" max="16" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="12" width="24" customWidth="1"/>
+    <col min="13" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Código no Domínio</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Código da Matriz</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Razão Social</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Nome Fantasia</v>
-      </c>
-      <c r="F1" t="str">
-        <v>CNPJ</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Regime Tributário</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Tipo de Fechamento</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Prazo de entrega do balancete</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Competência de início (mm/aaaa)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Fazer carga inicial de saldos</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Coleta automática do razão</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Sistema financeiro</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Integração financeira</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Analista responsável</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Observações</v>
-      </c>
+    <row r="1" ht="40" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>0370</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Matriz</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>Euro Brake Com. Imp. e Exp. LTDA</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Euro Brake</v>
-      </c>
-      <c r="F2" t="str">
-        <v>12.345.678/0001-90</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Lucro Real</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Consolidado + por filial</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Dia 10</v>
-      </c>
-      <c r="J2" t="str">
-        <v>01/2026</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Sim</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Sim</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Conta Azul</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Excel</v>
-      </c>
-      <c r="O2" t="str">
-        <v>João</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Cliente com 2 filiais</v>
+    <row r="3" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>0371</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Filial</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0370</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Euro Brake Com. Imp. e Exp. LTDA — Campinas</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Euro Brake Campinas</v>
-      </c>
-      <c r="F3" t="str">
-        <v>12.345.678/0002-71</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>0372</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Filial</v>
-      </c>
-      <c r="C4" t="str">
-        <v>0370</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Euro Brake Com. Imp. e Exp. LTDA — Joinville</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Euro Brake Joinville</v>
-      </c>
-      <c r="F4" t="str">
-        <v>12.345.678/0003-52</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="2:14" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="2:14" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B203">
+      <formula1>"Matriz,Filial"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B4:B203">
+      <formula1>"Matriz,Filial"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G203">
+      <formula1>"Simples,Presumido,Real"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G4:G203">
+      <formula1>"Simples,Presumido,Real"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I10:I203">
+      <formula1>"Dia 5,Dia 10,Dia 15,Dia 20,Dia 25,Dia 30"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I4:I203">
+      <formula1>"Dia 5,Dia 10,Dia 15,Dia 20,Dia 25,Dia 30"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K10:L203">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K4:L203">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="N10:N203">
+      <formula1>"Não usa,Sistema,Excel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="N4:N203">
+      <formula1>"Não usa,Sistema,Excel"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/modelo-importacao-clientes.xlsx
+++ b/public/modelo-importacao-clientes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Layout de Importação de Clientes — Contabilidade by Attentive</t>
   </si>
@@ -23,13 +23,16 @@
     <t>Preencha uma linha por empresa na aba “Clientes”. Não apague o cabeçalho.</t>
   </si>
   <si>
-    <t>Matriz e filiais ficam na mesma aba: a coluna “Tipo” diz se é Matriz ou Filial, e “Código da Matriz” liga a filial à matriz (deixe em branco na linha da matriz).</t>
+    <t>Matriz e filiais ficam na mesma aba: a coluna “Tipo” diz se é Matriz ou Filial, e “Código da Matriz” liga a filial à matriz (obrigatório na filial, em branco na matriz).</t>
   </si>
   <si>
     <t>CNPJ é a chave do cadastro — não é possível cadastrar dois clientes com o mesmo CNPJ.</t>
   </si>
   <si>
-    <t>Prazo de entrega do balancete: dia do mês (5, 10, 15, 20, 25 ou 30). É esse prazo que alimenta o painel de prazos do dashboard.</t>
+    <t>Tipo de fechamento: “Consolidado” = a filial fecha junto da matriz (não abre fechamento próprio); “Individualizado” = a filial tem fechamento próprio. Na matriz, use “Consolidado”.</t>
+  </si>
+  <si>
+    <t>Prazo de entrega do balancete: dia do mês (1 a 31). É esse prazo que alimenta o painel de prazos do dashboard.</t>
   </si>
   <si>
     <t>Sistema financeiro (coluna M): qual sistema o cliente usa — ex.: Conta Azul.</t>
@@ -541,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -585,6 +588,11 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +625,7 @@
     <row r="1" ht="40" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -637,52 +645,52 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25"/>
@@ -902,11 +910,11 @@
     <dataValidation type="list" allowBlank="1" sqref="G4:G203">
       <formula1>"Simples,Presumido,Real"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I10:I203">
-      <formula1>"Dia 5,Dia 10,Dia 15,Dia 20,Dia 25,Dia 30"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H203">
+      <formula1>"Consolidado,Individualizado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I4:I203">
-      <formula1>"Dia 5,Dia 10,Dia 15,Dia 20,Dia 25,Dia 30"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="H4:H203">
+      <formula1>"Consolidado,Individualizado"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="K10:L203">
       <formula1>"Sim,Não"</formula1>

--- a/public/modelo-importacao-clientes.xlsx
+++ b/public/modelo-importacao-clientes.xlsx
@@ -611,9 +611,7 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="6" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
     <col min="11" max="12" width="24" customWidth="1"/>
@@ -905,10 +903,10 @@
       <formula1>"Matriz,Filial"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G10:G203">
-      <formula1>"Simples,Presumido,Real"</formula1>
+      <formula1>"SIMPLES NACIONAL,LUCRO PRESUMIDO,LUCRO REAL,LUCRO REAL TRIMESTRAL,ISENTA FEDERAL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G4:G203">
-      <formula1>"Simples,Presumido,Real"</formula1>
+      <formula1>"SIMPLES NACIONAL,LUCRO PRESUMIDO,LUCRO REAL,LUCRO REAL TRIMESTRAL,ISENTA FEDERAL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H10:H203">
       <formula1>"Consolidado,Individualizado"</formula1>
